--- a/assets/docs/Ashraellen_Budget_2026_EN.xlsx
+++ b/assets/docs/Ashraellen_Budget_2026_EN.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8b277eb2e1374319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Budget" sheetId="2" r:id="Raef93b958eb14353"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" r:id="R78d2127dfc0a42ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production Assumptions" sheetId="4" r:id="R62904042bc284b8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R09cebbe38d9c475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R07df1994f4224610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Budget" sheetId="2" r:id="R2b630ede2a884558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" r:id="R61d20032941a4e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production Assumptions" sheetId="4" r:id="R355ed0510ab04cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R24ffa480b40b4225"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,13 +17,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="#,##0 €"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
+    <x:numFmt numFmtId="204" formatCode="0"/>
+    <x:numFmt numFmtId="205" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -57,8 +59,13 @@
       <x:color rgb="111827"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -85,6 +92,11 @@
         <x:fgColor rgb="FEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="E6F2FF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="20">
     <x:border/>
@@ -345,7 +357,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="72">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -484,6 +496,15 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -682,7 +703,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Annual budget for a multilingual literary-media research platform</x:v>
+        <x:v>Annual budget for a multilingual artistic-philosophical research platform</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -692,7 +713,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
-        <x:v>Main working scenario for twelve months of sustained writing, research, publication, translation, video/audio production and platform development.</x:v>
+        <x:v>Main working scenario for twelve months of sustained artistic research, writing, editing, publication, translation, video/audio forms and platform development. The infrastructure serves the research, not the other way around.</x:v>
       </x:c>
       <x:c r="B4" s="17"/>
       <x:c r="C4" s="17"/>
@@ -724,7 +745,7 @@
         <x:v>Living support</x:v>
       </x:c>
       <x:c r="B8" s="44" t="str">
-        <x:v>Basic living support required to secure sustained working time for writing, research, editing and platform development.</x:v>
+        <x:v>Basic living support required to secure sustained working time for artistic-philosophical research, writing, editing and platform development.</x:v>
       </x:c>
       <x:c r="C8" s="45" t="n">
         <x:v>24000</x:v>
@@ -735,7 +756,7 @@
         <x:v>Digital tools and AI production</x:v>
       </x:c>
       <x:c r="B9" s="44" t="str">
-        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, editing/SEO tools and technical subscriptions.</x:v>
+        <x:v>AI, voice, coding, translation, editing and technical tools used as infrastructure for recording and sharing the research across languages and formats.</x:v>
       </x:c>
       <x:c r="C9" s="45" t="n">
         <x:v>17004</x:v>
@@ -746,7 +767,7 @@
         <x:v>Video template/render infrastructure</x:v>
       </x:c>
       <x:c r="B10" s="44" t="str">
-        <x:v>Remotion-based reusable video templates, local rendering setup, testing and small render/cloud reserve.</x:v>
+        <x:v>Reusable Remotion templates, local rendering setup, testing and small render/cloud reserve for regular public forms of the research.</x:v>
       </x:c>
       <x:c r="C10" s="45" t="n">
         <x:v>600</x:v>
@@ -757,7 +778,7 @@
         <x:v>Equipment / workstation setup</x:v>
       </x:c>
       <x:c r="B11" s="44" t="str">
-        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for video and publishing work.</x:v>
+        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for editing, publication and multilingual archive work.</x:v>
       </x:c>
       <x:c r="C11" s="45" t="n">
         <x:v>6000</x:v>
@@ -768,7 +789,7 @@
         <x:v>Internet, backup and technical reserve</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
-        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity.</x:v>
+        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity for preserving the archive and working materials.</x:v>
       </x:c>
       <x:c r="C12" s="45" t="n">
         <x:v>2000</x:v>
@@ -814,7 +835,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5145304e1e6a4360"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ad6b736c76c4a73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -841,7 +862,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Annual budget for a multilingual literary-media research platform</x:v>
+        <x:v>Annual budget for a multilingual artistic-philosophical research platform</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -868,7 +889,7 @@
         <x:v>Living support</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Basic living support required to secure sustained working time for writing, research, editing and platform development.</x:v>
+        <x:v>Basic living support required to secure sustained working time for artistic-philosophical research, writing, editing and platform development.</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
         <x:v>24000</x:v>
@@ -883,7 +904,7 @@
         <x:v>Digital tools and AI production</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, editing/SEO tools and technical subscriptions.</x:v>
+        <x:v>AI, voice, coding, translation, editing and technical tools used as infrastructure for recording and sharing the research across languages and formats.</x:v>
       </x:c>
       <x:c r="C6" s="28" t="n">
         <x:v>17004</x:v>
@@ -898,7 +919,7 @@
         <x:v>Video template/render infrastructure</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Remotion-based reusable video templates, local rendering setup, testing and small render/cloud reserve.</x:v>
+        <x:v>Reusable Remotion templates, local rendering setup, testing and small render/cloud reserve for regular public forms of the research.</x:v>
       </x:c>
       <x:c r="C7" s="28" t="n">
         <x:v>600</x:v>
@@ -913,7 +934,7 @@
         <x:v>Equipment / workstation setup</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for video and publishing work.</x:v>
+        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for editing, publication and multilingual archive work.</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:v>6000</x:v>
@@ -928,7 +949,7 @@
         <x:v>Internet, backup and technical reserve</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity.</x:v>
+        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity for preserving the archive and working materials.</x:v>
       </x:c>
       <x:c r="C9" s="28" t="n">
         <x:v>2000</x:v>
@@ -989,7 +1010,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ceecf3acc754809"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc24273947c664180"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1188,7 +1209,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Voice, video and multilingual production assumptions</x:v>
+        <x:v>Voice, video and multilingual production assumptions for public forms of the research</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -1244,7 +1265,7 @@
       <x:c r="A8" s="11" t="str">
         <x:v>Long-form voice minutes per month</x:v>
       </x:c>
-      <x:c r="B8" s="68" t="n">
+      <x:c r="B8" s="75" t="n">
         <x:f>B5*B6*B7</x:f>
         <x:v>1890</x:v>
       </x:c>
@@ -1256,7 +1277,7 @@
       <x:c r="A9" s="11" t="str">
         <x:v>Saint Whine Shorts per month</x:v>
       </x:c>
-      <x:c r="B9" s="68" t="n">
+      <x:c r="B9" s="75" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
@@ -1267,7 +1288,7 @@
       <x:c r="A10" s="11" t="str">
         <x:v>Average Short duration (minutes)</x:v>
       </x:c>
-      <x:c r="B10" s="68" t="n">
+      <x:c r="B10" s="75" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
@@ -1278,7 +1299,7 @@
       <x:c r="A11" s="11" t="str">
         <x:v>Languages for Shorts baseline</x:v>
       </x:c>
-      <x:c r="B11" s="68" t="n">
+      <x:c r="B11" s="75" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
@@ -1289,7 +1310,7 @@
       <x:c r="A12" s="11" t="str">
         <x:v>Shorts voice minutes per month</x:v>
       </x:c>
-      <x:c r="B12" s="68" t="n">
+      <x:c r="B12" s="75" t="n">
         <x:f>B9*B10*B11</x:f>
         <x:v>30</x:v>
       </x:c>
@@ -1301,7 +1322,7 @@
       <x:c r="A13" s="11" t="str">
         <x:v>Regeneration/testing reserve</x:v>
       </x:c>
-      <x:c r="B13" s="69" t="n">
+      <x:c r="B13" s="76" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
@@ -1312,19 +1333,19 @@
       <x:c r="A14" s="11" t="str">
         <x:v>Estimated voice minutes incl. reserve</x:v>
       </x:c>
-      <x:c r="B14" s="69" t="n">
+      <x:c r="B14" s="75" t="n">
         <x:f>(B8+B12)*(1+B13)</x:f>
         <x:v>2304</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>Large videos + Shorts + 20% reserve</x:v>
+        <x:v>(1,890 + 30) × 1.2 = 2,304 minutes/month</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>ElevenLabs Business approximate monthly capacity</x:v>
       </x:c>
-      <x:c r="B15" s="69" t="n">
+      <x:c r="B15" s="75" t="n">
         <x:v>6000</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
@@ -1335,13 +1356,34 @@
       <x:c r="A16" s="11" t="str">
         <x:v>Estimated monthly capacity buffer</x:v>
       </x:c>
-      <x:c r="B16" s="69" t="n">
+      <x:c r="B16" s="75" t="n">
         <x:f>B15-B14</x:f>
         <x:v>3696</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>Approximate unused capacity for tests, extra Shorts and growth</x:v>
       </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="74" t="str">
+        <x:v>Budget hierarchy</x:v>
+      </x:c>
+      <x:c r="B18" s="74"/>
+      <x:c r="C18" s="74"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="11" t="str">
+        <x:v>mode of seeing → inquiry into meaning → forms of recording → public platform → production infrastructure</x:v>
+      </x:c>
+      <x:c r="B19" s="11"/>
+      <x:c r="C19" s="11"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="11" t="str">
+        <x:v>The infrastructure serves the research. The budget is not a media-production wishlist, but the working base for preserving, translating and sharing the research.</x:v>
+      </x:c>
+      <x:c r="B20" s="11"/>
+      <x:c r="C20" s="11"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/assets/docs/Ashraellen_Budget_2026_EN.xlsx
+++ b/assets/docs/Ashraellen_Budget_2026_EN.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R07df1994f4224610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Budget" sheetId="2" r:id="R2b630ede2a884558"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" r:id="R61d20032941a4e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production Assumptions" sheetId="4" r:id="R355ed0510ab04cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R24ffa480b40b4225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1d5c3df1640642d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Budget" sheetId="2" r:id="R054d6dab9e5c45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" r:id="R38f81bf592bb4533"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production Assumptions" sheetId="4" r:id="R6fa100c0952c4e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Ra9102be4f87d4161"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -713,7 +713,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
-        <x:v>Main working scenario for twelve months of sustained artistic research, writing, editing, publication, translation, video/audio forms and platform development. The infrastructure serves the research, not the other way around.</x:v>
+        <x:v>Main working scenario for twelve months of sustained artistic research, writing, editing, publication, translation, video/audio forms and platform development. The requested infrastructure is the working base for preserving, translating and sharing the research.</x:v>
       </x:c>
       <x:c r="B4" s="17"/>
       <x:c r="C4" s="17"/>
@@ -835,7 +835,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ad6b736c76c4a73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b8c1f85676b436d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1010,7 +1010,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc24273947c664180"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf2066a0c01e425a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1380,7 +1380,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>The infrastructure serves the research. The budget is not a media-production wishlist, but the working base for preserving, translating and sharing the research.</x:v>
+        <x:v>The infrastructure is the working base for preserving, translating and sharing the research in literary, audio, video and multilingual formats.</x:v>
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="11"/>

--- a/assets/docs/Ashraellen_Budget_2026_EN.xlsx
+++ b/assets/docs/Ashraellen_Budget_2026_EN.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1d5c3df1640642d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Budget" sheetId="2" r:id="R054d6dab9e5c45bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" r:id="R38f81bf592bb4533"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production Assumptions" sheetId="4" r:id="R6fa100c0952c4e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Ra9102be4f87d4161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8b277eb2e1374319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Budget" sheetId="2" r:id="Raef93b958eb14353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" r:id="R78d2127dfc0a42ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production Assumptions" sheetId="4" r:id="R62904042bc284b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R09cebbe38d9c475c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,15 +17,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="#,##0 €"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0"/>
-    <x:numFmt numFmtId="205" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,13 +57,8 @@
       <x:color rgb="111827"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,11 +85,6 @@
         <x:fgColor rgb="FEF3C7"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="E6F2FF"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="20">
     <x:border/>
@@ -357,7 +345,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -496,15 +484,6 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -703,7 +682,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Annual budget for a multilingual artistic-philosophical research platform</x:v>
+        <x:v>Annual budget for a multilingual literary-media research platform</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -713,7 +692,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
-        <x:v>Main working scenario for twelve months of sustained artistic research, writing, editing, publication, translation, video/audio forms and platform development. The requested infrastructure is the working base for preserving, translating and sharing the research.</x:v>
+        <x:v>Main working scenario for twelve months of sustained writing, research, publication, translation, video/audio production and platform development.</x:v>
       </x:c>
       <x:c r="B4" s="17"/>
       <x:c r="C4" s="17"/>
@@ -745,7 +724,7 @@
         <x:v>Living support</x:v>
       </x:c>
       <x:c r="B8" s="44" t="str">
-        <x:v>Basic living support required to secure sustained working time for artistic-philosophical research, writing, editing and platform development.</x:v>
+        <x:v>Basic living support required to secure sustained working time for writing, research, editing and platform development.</x:v>
       </x:c>
       <x:c r="C8" s="45" t="n">
         <x:v>24000</x:v>
@@ -756,7 +735,7 @@
         <x:v>Digital tools and AI production</x:v>
       </x:c>
       <x:c r="B9" s="44" t="str">
-        <x:v>AI, voice, coding, translation, editing and technical tools used as infrastructure for recording and sharing the research across languages and formats.</x:v>
+        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, editing/SEO tools and technical subscriptions.</x:v>
       </x:c>
       <x:c r="C9" s="45" t="n">
         <x:v>17004</x:v>
@@ -767,7 +746,7 @@
         <x:v>Video template/render infrastructure</x:v>
       </x:c>
       <x:c r="B10" s="44" t="str">
-        <x:v>Reusable Remotion templates, local rendering setup, testing and small render/cloud reserve for regular public forms of the research.</x:v>
+        <x:v>Remotion-based reusable video templates, local rendering setup, testing and small render/cloud reserve.</x:v>
       </x:c>
       <x:c r="C10" s="45" t="n">
         <x:v>600</x:v>
@@ -778,7 +757,7 @@
         <x:v>Equipment / workstation setup</x:v>
       </x:c>
       <x:c r="B11" s="44" t="str">
-        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for editing, publication and multilingual archive work.</x:v>
+        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for video and publishing work.</x:v>
       </x:c>
       <x:c r="C11" s="45" t="n">
         <x:v>6000</x:v>
@@ -789,7 +768,7 @@
         <x:v>Internet, backup and technical reserve</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
-        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity for preserving the archive and working materials.</x:v>
+        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity.</x:v>
       </x:c>
       <x:c r="C12" s="45" t="n">
         <x:v>2000</x:v>
@@ -835,7 +814,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b8c1f85676b436d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5145304e1e6a4360"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -862,7 +841,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Annual budget for a multilingual artistic-philosophical research platform</x:v>
+        <x:v>Annual budget for a multilingual literary-media research platform</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -889,7 +868,7 @@
         <x:v>Living support</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Basic living support required to secure sustained working time for artistic-philosophical research, writing, editing and platform development.</x:v>
+        <x:v>Basic living support required to secure sustained working time for writing, research, editing and platform development.</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
         <x:v>24000</x:v>
@@ -904,7 +883,7 @@
         <x:v>Digital tools and AI production</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>AI, voice, coding, translation, editing and technical tools used as infrastructure for recording and sharing the research across languages and formats.</x:v>
+        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, editing/SEO tools and technical subscriptions.</x:v>
       </x:c>
       <x:c r="C6" s="28" t="n">
         <x:v>17004</x:v>
@@ -919,7 +898,7 @@
         <x:v>Video template/render infrastructure</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Reusable Remotion templates, local rendering setup, testing and small render/cloud reserve for regular public forms of the research.</x:v>
+        <x:v>Remotion-based reusable video templates, local rendering setup, testing and small render/cloud reserve.</x:v>
       </x:c>
       <x:c r="C7" s="28" t="n">
         <x:v>600</x:v>
@@ -934,7 +913,7 @@
         <x:v>Equipment / workstation setup</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for editing, publication and multilingual archive work.</x:v>
+        <x:v>Powerful laptop/workstation, wide monitor, external SSD/backup drive, hub/peripherals for video and publishing work.</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:v>6000</x:v>
@@ -949,7 +928,7 @@
         <x:v>Internet, backup and technical reserve</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity for preserving the archive and working materials.</x:v>
+        <x:v>Stable connection, mobile/travel internet reserve, backups, storage overflow and technical continuity.</x:v>
       </x:c>
       <x:c r="C9" s="28" t="n">
         <x:v>2000</x:v>
@@ -1010,7 +989,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf2066a0c01e425a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ceecf3acc754809"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1209,7 +1188,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Voice, video and multilingual production assumptions for public forms of the research</x:v>
+        <x:v>Voice, video and multilingual production assumptions</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -1265,7 +1244,7 @@
       <x:c r="A8" s="11" t="str">
         <x:v>Long-form voice minutes per month</x:v>
       </x:c>
-      <x:c r="B8" s="75" t="n">
+      <x:c r="B8" s="68" t="n">
         <x:f>B5*B6*B7</x:f>
         <x:v>1890</x:v>
       </x:c>
@@ -1277,7 +1256,7 @@
       <x:c r="A9" s="11" t="str">
         <x:v>Saint Whine Shorts per month</x:v>
       </x:c>
-      <x:c r="B9" s="75" t="n">
+      <x:c r="B9" s="68" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
@@ -1288,7 +1267,7 @@
       <x:c r="A10" s="11" t="str">
         <x:v>Average Short duration (minutes)</x:v>
       </x:c>
-      <x:c r="B10" s="75" t="n">
+      <x:c r="B10" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
@@ -1299,7 +1278,7 @@
       <x:c r="A11" s="11" t="str">
         <x:v>Languages for Shorts baseline</x:v>
       </x:c>
-      <x:c r="B11" s="75" t="n">
+      <x:c r="B11" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
@@ -1310,7 +1289,7 @@
       <x:c r="A12" s="11" t="str">
         <x:v>Shorts voice minutes per month</x:v>
       </x:c>
-      <x:c r="B12" s="75" t="n">
+      <x:c r="B12" s="68" t="n">
         <x:f>B9*B10*B11</x:f>
         <x:v>30</x:v>
       </x:c>
@@ -1322,7 +1301,7 @@
       <x:c r="A13" s="11" t="str">
         <x:v>Regeneration/testing reserve</x:v>
       </x:c>
-      <x:c r="B13" s="76" t="n">
+      <x:c r="B13" s="69" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
@@ -1333,19 +1312,19 @@
       <x:c r="A14" s="11" t="str">
         <x:v>Estimated voice minutes incl. reserve</x:v>
       </x:c>
-      <x:c r="B14" s="75" t="n">
+      <x:c r="B14" s="69" t="n">
         <x:f>(B8+B12)*(1+B13)</x:f>
         <x:v>2304</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>(1,890 + 30) × 1.2 = 2,304 minutes/month</x:v>
+        <x:v>Large videos + Shorts + 20% reserve</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>ElevenLabs Business approximate monthly capacity</x:v>
       </x:c>
-      <x:c r="B15" s="75" t="n">
+      <x:c r="B15" s="69" t="n">
         <x:v>6000</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
@@ -1356,34 +1335,13 @@
       <x:c r="A16" s="11" t="str">
         <x:v>Estimated monthly capacity buffer</x:v>
       </x:c>
-      <x:c r="B16" s="75" t="n">
+      <x:c r="B16" s="69" t="n">
         <x:f>B15-B14</x:f>
         <x:v>3696</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>Approximate unused capacity for tests, extra Shorts and growth</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="74" t="str">
-        <x:v>Budget hierarchy</x:v>
-      </x:c>
-      <x:c r="B18" s="74"/>
-      <x:c r="C18" s="74"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="11" t="str">
-        <x:v>mode of seeing → inquiry into meaning → forms of recording → public platform → production infrastructure</x:v>
-      </x:c>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="11"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="11" t="str">
-        <x:v>The infrastructure is the working base for preserving, translating and sharing the research in literary, audio, video and multilingual formats.</x:v>
-      </x:c>
-      <x:c r="B20" s="11"/>
-      <x:c r="C20" s="11"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
